--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -21409,13 +21409,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CECA1B4-E459-4C24-95BE-A81C4DD38860}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5B0ACD4-0672-4C63-8DB4-136DA76FF7A4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C38D4804-851B-4F26-B650-FBA3406E8C79}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B15C12D-9A50-4A26-B553-522127A7BA02}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2CD1D0F-F0AC-4D31-9951-534EC65EDC62}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B75EA9A-9FD2-4E98-8F0C-1A3276B342E7}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -21409,13 +21409,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5B0ACD4-0672-4C63-8DB4-136DA76FF7A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E9FE9C6-8D35-458B-B146-7A1B96BDC2F7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B15C12D-9A50-4A26-B553-522127A7BA02}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C9BB76F-E97D-4FF1-B911-C0DEAC24E91D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B75EA9A-9FD2-4E98-8F0C-1A3276B342E7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08D37939-A9C6-4284-A740-DF9C5DC238C1}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -21409,13 +21409,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E9FE9C6-8D35-458B-B146-7A1B96BDC2F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D2CC40C-9969-4A2E-B5F9-F461C8595DAC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C9BB76F-E97D-4FF1-B911-C0DEAC24E91D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0ECFEFB-4C02-4CA9-A08A-B61669781FB6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08D37939-A9C6-4284-A740-DF9C5DC238C1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A24CB55-54BE-47F0-8147-3B079BE0BE93}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -21409,13 +21409,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D2CC40C-9969-4A2E-B5F9-F461C8595DAC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6AC06CB-0CDA-45EE-8205-2CC574BA091A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0ECFEFB-4C02-4CA9-A08A-B61669781FB6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7E91736-B30C-487F-8231-B651F704AA51}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A24CB55-54BE-47F0-8147-3B079BE0BE93}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF5D99A-AEFB-4FDE-976A-5DB0B1188C98}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -21400,22 +21400,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6AC06CB-0CDA-45EE-8205-2CC574BA091A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAB85173-34EB-484A-86D1-B9560DAB64ED}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7E91736-B30C-487F-8231-B651F704AA51}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28828D40-3F80-4F12-80D1-3CF2675CE1FC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF5D99A-AEFB-4FDE-976A-5DB0B1188C98}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5FBFD39-B8D9-4C52-8F6E-6097113112F9}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -21400,22 +21400,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D2CC40C-9969-4A2E-B5F9-F461C8595DAC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A31C0AE5-4CE8-4886-9A96-D874C8B4DD8A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0ECFEFB-4C02-4CA9-A08A-B61669781FB6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3434F78D-BC63-4921-B3B9-BE34827C32DD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A24CB55-54BE-47F0-8147-3B079BE0BE93}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4395B66-AB18-4836-A4A9-C54D277206E3}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -21409,13 +21409,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAB85173-34EB-484A-86D1-B9560DAB64ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{452BDA5A-15E6-4D20-990A-922D630F3BE4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28828D40-3F80-4F12-80D1-3CF2675CE1FC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8DB2144-3008-4070-9F88-332101920C12}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5FBFD39-B8D9-4C52-8F6E-6097113112F9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{427CC5EF-4D12-46A0-9150-6EDA708C1A47}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -21409,13 +21409,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{452BDA5A-15E6-4D20-990A-922D630F3BE4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40CD1517-E299-4F34-9367-E2A63030A787}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8DB2144-3008-4070-9F88-332101920C12}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADE1090A-5B89-4B51-B434-081FC34F2EAB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{427CC5EF-4D12-46A0-9150-6EDA708C1A47}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80F6569F-F39E-4FE3-913C-B0F576172388}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -21409,13 +21409,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40CD1517-E299-4F34-9367-E2A63030A787}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F61C009-3A1A-460A-B3C5-4555C285FC6B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADE1090A-5B89-4B51-B434-081FC34F2EAB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75342835-207E-4DAC-9906-D118D4C8CF39}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80F6569F-F39E-4FE3-913C-B0F576172388}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{293DA830-021E-4944-A36D-0110226FDEAA}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -21409,13 +21409,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F61C009-3A1A-460A-B3C5-4555C285FC6B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEA2459E-1BD0-4866-A719-ACD195631625}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75342835-207E-4DAC-9906-D118D4C8CF39}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C7E144B-97D6-425E-8671-B1C6115FE703}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{293DA830-021E-4944-A36D-0110226FDEAA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27790295-59DD-4B09-84AB-24B9C0F5253C}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -22285,13 +22285,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1823BA0E-F25F-4946-A23A-52ACDD18803A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9822FEC3-AA9A-4EEA-9DD7-DFC7ED24AAD6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D68B4F54-6682-4D5F-BD35-FDBAC9DD7A89}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82956A3-C72A-4CDD-B7AD-3C4834F02D33}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EA26257-4235-4791-8B63-531594742A2E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{626FE6CA-EED1-4982-82FF-3FAD8C1CA932}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -22285,13 +22285,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9822FEC3-AA9A-4EEA-9DD7-DFC7ED24AAD6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F650A340-1882-4117-A3B0-E1BB3EEC36D6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82956A3-C72A-4CDD-B7AD-3C4834F02D33}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E21D9C9-F848-4781-9DFC-711667704303}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{626FE6CA-EED1-4982-82FF-3FAD8C1CA932}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FE2BDBC-FCFE-40AE-BC9B-8E7176324646}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -22285,13 +22285,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F650A340-1882-4117-A3B0-E1BB3EEC36D6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64856542-0C4F-43C0-AB33-97DFEF9ECA57}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E21D9C9-F848-4781-9DFC-711667704303}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13273046-6132-431E-B572-45CF37AABC16}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FE2BDBC-FCFE-40AE-BC9B-8E7176324646}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B12B0A22-B609-4104-BC1C-06E45B5C7203}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -22285,13 +22285,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64856542-0C4F-43C0-AB33-97DFEF9ECA57}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3EB3CA0-D0C7-4DAC-99AD-816486517A20}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13273046-6132-431E-B572-45CF37AABC16}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC5A4D05-467A-4ADC-BD91-FEE5186C8EC3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B12B0A22-B609-4104-BC1C-06E45B5C7203}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16608F22-7A9E-4EA6-8107-541E97526D8D}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -22285,13 +22285,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3EB3CA0-D0C7-4DAC-99AD-816486517A20}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85B853A8-0B6B-46A9-B233-91E2DCCF4C83}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC5A4D05-467A-4ADC-BD91-FEE5186C8EC3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D37D6EEC-E2DC-404A-93B1-812AE322F5A1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16608F22-7A9E-4EA6-8107-541E97526D8D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE95B1F8-1E78-4546-A44B-AF6C39FADBD1}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -22285,13 +22285,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85B853A8-0B6B-46A9-B233-91E2DCCF4C83}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88A4E230-5990-493D-A526-DD92981DAA46}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D37D6EEC-E2DC-404A-93B1-812AE322F5A1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F7B6817-124A-4CF2-938A-AC8AD2D90410}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE95B1F8-1E78-4546-A44B-AF6C39FADBD1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50C839E2-679D-4FDC-B188-4A62E8C91858}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -22285,13 +22285,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88A4E230-5990-493D-A526-DD92981DAA46}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2DC4ED0-84A4-425E-9EB2-B8EB9A5DDA18}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F7B6817-124A-4CF2-938A-AC8AD2D90410}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78FD230F-D630-405D-9754-AD2222092225}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50C839E2-679D-4FDC-B188-4A62E8C91858}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AC6E778-0DB5-49DB-BA21-967B72B61375}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -22285,13 +22285,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2DC4ED0-84A4-425E-9EB2-B8EB9A5DDA18}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05EA705F-C77B-4CFD-AA3B-52015AE91A90}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78FD230F-D630-405D-9754-AD2222092225}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7856AE34-DF78-453C-91AB-28D3D78E5915}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AC6E778-0DB5-49DB-BA21-967B72B61375}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A51378D3-288F-4FA6-B380-A8A83E8A4724}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -22285,13 +22285,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05EA705F-C77B-4CFD-AA3B-52015AE91A90}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{437229CF-D6C5-4DDA-8546-93D5AE2B53CA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7856AE34-DF78-453C-91AB-28D3D78E5915}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C31C8EA-3F0B-4691-A62A-1BD5E2B0FF68}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A51378D3-288F-4FA6-B380-A8A83E8A4724}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B9CE04F-3316-43F7-BF07-B86CF0A1E156}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -22285,13 +22285,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{437229CF-D6C5-4DDA-8546-93D5AE2B53CA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7738A785-C2F6-4AB4-950C-491C554D96B5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C31C8EA-3F0B-4691-A62A-1BD5E2B0FF68}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{874B27ED-EE2D-444C-8D8A-0024FE4E93A5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B9CE04F-3316-43F7-BF07-B86CF0A1E156}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AB692AD-A3DF-4155-95E6-B6DAAECD1E14}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -22285,13 +22285,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7738A785-C2F6-4AB4-950C-491C554D96B5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2ABDBB50-EAA5-4AF2-9346-6F475CAB2FB8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{874B27ED-EE2D-444C-8D8A-0024FE4E93A5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{152B45D2-8152-47EF-9E8C-15B0166BA401}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AB692AD-A3DF-4155-95E6-B6DAAECD1E14}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3571151-1A50-41FE-A89F-23C9579173FE}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -22285,13 +22285,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2ABDBB50-EAA5-4AF2-9346-6F475CAB2FB8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52066D77-2B80-4DCC-88D6-DB6CC2B18E8B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{152B45D2-8152-47EF-9E8C-15B0166BA401}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2DFFF06-7219-41BA-8760-99B93F2F8EAD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3571151-1A50-41FE-A89F-23C9579173FE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA0D2ACF-F149-4405-8670-02337C8F00B6}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -22285,13 +22285,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52066D77-2B80-4DCC-88D6-DB6CC2B18E8B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B9EA615-9025-4D40-8C82-9F172E7AACEB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2DFFF06-7219-41BA-8760-99B93F2F8EAD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{803B3A7D-E0EC-47E9-9462-1509E2BCD0BF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA0D2ACF-F149-4405-8670-02337C8F00B6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FAE39C9-B2B8-41FF-BD21-9D1821724AE3}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -22285,13 +22285,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B9EA615-9025-4D40-8C82-9F172E7AACEB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{522E7025-77BF-4BB9-9FA5-2B1B31E23EA6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{803B3A7D-E0EC-47E9-9462-1509E2BCD0BF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06502859-C51A-4869-9416-47B99330D8F3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FAE39C9-B2B8-41FF-BD21-9D1821724AE3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A257A023-4FB0-48CE-AD1D-212F1E3B25AE}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -22285,13 +22285,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{522E7025-77BF-4BB9-9FA5-2B1B31E23EA6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{383D8F07-8CD3-4958-98B1-6E8C9D25065F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06502859-C51A-4869-9416-47B99330D8F3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0835F91C-153B-4496-A0AF-643EE7D56D8E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A257A023-4FB0-48CE-AD1D-212F1E3B25AE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B56BE00-2134-4326-AA08-8D5DC59646D0}"/>
 </file>